--- a/extra/IHME_GBD_2023_COD_CAUSE_ICD_CODE_MAP_Y2025M10D12.XLSX
+++ b/extra/IHME_GBD_2023_COD_CAUSE_ICD_CODE_MAP_Y2025M10D12.XLSX
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\team\cod\pub\cod_team\mwcunnin\gbd2023_resubmission_figures\proofs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DATA\recod_GC\extra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A776F9-AF02-48AF-9300-244692B61F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F20FD6-795C-4933-8C98-7C230B7434D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$2</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -2648,7 +2648,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2675,6 +2675,13 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2763,7 +2770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2779,6 +2786,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3088,19 +3101,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C311"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="40.6640625" customWidth="1"/>
+    <col min="1" max="3" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>872</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3111,7 +3124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="288.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="288.60000000000002" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -3122,18 +3135,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -3144,7 +3157,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -3155,7 +3168,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -3166,7 +3179,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -3177,7 +3190,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -3188,7 +3201,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
@@ -3199,7 +3212,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -3210,7 +3223,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
@@ -3221,7 +3234,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -3232,7 +3245,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>30</v>
       </c>
@@ -3243,18 +3256,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="51" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>36</v>
       </c>
@@ -3265,7 +3278,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>39</v>
       </c>
@@ -3276,7 +3289,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
@@ -3287,7 +3300,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>43</v>
       </c>
@@ -3298,7 +3311,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>44</v>
       </c>
@@ -3309,7 +3322,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>47</v>
       </c>
@@ -3320,7 +3333,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>50</v>
       </c>
@@ -3331,7 +3344,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>53</v>
       </c>
@@ -3342,7 +3355,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>56</v>
       </c>
@@ -3353,7 +3366,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>59</v>
       </c>
@@ -3364,7 +3377,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>62</v>
       </c>
@@ -3375,7 +3388,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>65</v>
       </c>
@@ -3386,7 +3399,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>68</v>
       </c>
@@ -3397,18 +3410,18 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="7" t="s">
         <v>72</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>74</v>
       </c>
@@ -3419,7 +3432,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>77</v>
       </c>
@@ -3430,7 +3443,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>80</v>
       </c>
@@ -3441,7 +3454,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>83</v>
       </c>
@@ -3452,7 +3465,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>86</v>
       </c>
@@ -3463,7 +3476,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>89</v>
       </c>
@@ -3474,7 +3487,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>92</v>
       </c>
@@ -3485,18 +3498,18 @@
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="51" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="7" t="s">
         <v>96</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>98</v>
       </c>
@@ -3507,7 +3520,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>101</v>
       </c>
@@ -3518,7 +3531,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>104</v>
       </c>
@@ -3529,7 +3542,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>107</v>
       </c>
@@ -3540,7 +3553,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>108</v>
       </c>
@@ -3551,7 +3564,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>111</v>
       </c>
@@ -3562,7 +3575,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>114</v>
       </c>
@@ -3573,7 +3586,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>117</v>
       </c>
@@ -3584,7 +3597,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>120</v>
       </c>
@@ -3595,7 +3608,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>123</v>
       </c>
@@ -3606,7 +3619,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>126</v>
       </c>
@@ -3617,7 +3630,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>129</v>
       </c>
@@ -3628,7 +3641,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>132</v>
       </c>
@@ -3639,7 +3652,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>133</v>
       </c>
@@ -3650,7 +3663,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>135</v>
       </c>
@@ -3661,7 +3674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>137</v>
       </c>
@@ -3672,18 +3685,18 @@
         <v>139</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="81.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
+    <row r="54" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="6" t="s">
         <v>141</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>143</v>
       </c>
@@ -3694,7 +3707,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>146</v>
       </c>
@@ -3705,7 +3718,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>149</v>
       </c>
@@ -3716,7 +3729,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>152</v>
       </c>
@@ -3727,7 +3740,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>155</v>
       </c>
@@ -3738,7 +3751,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>158</v>
       </c>
@@ -3749,7 +3762,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>161</v>
       </c>
@@ -3760,7 +3773,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>164</v>
       </c>
@@ -3771,7 +3784,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>167</v>
       </c>
@@ -3782,7 +3795,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>170</v>
       </c>
@@ -3793,7 +3806,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>173</v>
       </c>
@@ -3804,7 +3817,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>174</v>
       </c>
@@ -3815,7 +3828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="71.400000000000006" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>176</v>
       </c>
@@ -3826,7 +3839,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>179</v>
       </c>
@@ -3837,7 +3850,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>182</v>
       </c>
@@ -3848,7 +3861,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>185</v>
       </c>
@@ -3859,7 +3872,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>188</v>
       </c>
@@ -3870,7 +3883,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>191</v>
       </c>
@@ -3881,7 +3894,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>194</v>
       </c>
@@ -3892,7 +3905,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>197</v>
       </c>
@@ -3903,7 +3916,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>200</v>
       </c>
@@ -3914,7 +3927,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>203</v>
       </c>
@@ -3925,7 +3938,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>206</v>
       </c>
@@ -3936,7 +3949,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>208</v>
       </c>
@@ -3947,7 +3960,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>209</v>
       </c>
@@ -3958,7 +3971,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>212</v>
       </c>
@@ -3969,7 +3982,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>215</v>
       </c>
@@ -3980,7 +3993,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>218</v>
       </c>
@@ -3991,7 +4004,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>221</v>
       </c>
@@ -4002,7 +4015,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>224</v>
       </c>
@@ -4013,7 +4026,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>227</v>
       </c>
@@ -4024,7 +4037,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>230</v>
       </c>
@@ -4035,7 +4048,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>233</v>
       </c>
@@ -4046,7 +4059,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>236</v>
       </c>
@@ -4057,7 +4070,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>239</v>
       </c>
@@ -4068,7 +4081,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="122.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="168.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>242</v>
       </c>
@@ -4079,7 +4092,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>245</v>
       </c>
@@ -4090,7 +4103,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>248</v>
       </c>
@@ -4101,7 +4114,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>251</v>
       </c>
@@ -4112,7 +4125,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>254</v>
       </c>
@@ -4123,7 +4136,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>257</v>
       </c>
@@ -4134,7 +4147,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>260</v>
       </c>
@@ -4145,7 +4158,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>263</v>
       </c>
@@ -4156,7 +4169,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>266</v>
       </c>
@@ -4167,7 +4180,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>267</v>
       </c>
@@ -4178,7 +4191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>268</v>
       </c>
@@ -4189,7 +4202,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>269</v>
       </c>
@@ -4200,7 +4213,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>270</v>
       </c>
@@ -4211,7 +4224,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>272</v>
       </c>
@@ -4222,7 +4235,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>273</v>
       </c>
@@ -4233,7 +4246,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>276</v>
       </c>
@@ -4244,7 +4257,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>279</v>
       </c>
@@ -4255,7 +4268,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>282</v>
       </c>
@@ -4266,7 +4279,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>285</v>
       </c>
@@ -4277,7 +4290,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>288</v>
       </c>
@@ -4288,7 +4301,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>291</v>
       </c>
@@ -4299,7 +4312,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>293</v>
       </c>
@@ -4310,7 +4323,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>296</v>
       </c>
@@ -4321,7 +4334,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>299</v>
       </c>
@@ -4332,7 +4345,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>302</v>
       </c>
@@ -4343,7 +4356,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>305</v>
       </c>
@@ -4354,7 +4367,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>308</v>
       </c>
@@ -4365,7 +4378,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>311</v>
       </c>
@@ -4376,7 +4389,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>314</v>
       </c>
@@ -4387,7 +4400,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>317</v>
       </c>
@@ -4398,7 +4411,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>320</v>
       </c>
@@ -4409,7 +4422,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>323</v>
       </c>
@@ -4420,7 +4433,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>326</v>
       </c>
@@ -4431,7 +4444,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>329</v>
       </c>
@@ -4442,7 +4455,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>332</v>
       </c>
@@ -4453,7 +4466,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>335</v>
       </c>
@@ -4464,7 +4477,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>337</v>
       </c>
@@ -4475,7 +4488,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>340</v>
       </c>
@@ -4486,7 +4499,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>342</v>
       </c>
@@ -4497,7 +4510,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>345</v>
       </c>
@@ -4508,7 +4521,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>348</v>
       </c>
@@ -4519,7 +4532,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>351</v>
       </c>
@@ -4530,7 +4543,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>354</v>
       </c>
@@ -4541,7 +4554,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>357</v>
       </c>
@@ -4552,7 +4565,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>360</v>
       </c>
@@ -4563,7 +4576,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>363</v>
       </c>
@@ -4574,7 +4587,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>364</v>
       </c>
@@ -4585,7 +4598,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>367</v>
       </c>
@@ -4596,7 +4609,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>370</v>
       </c>
@@ -4607,7 +4620,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>373</v>
       </c>
@@ -4618,7 +4631,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>376</v>
       </c>
@@ -4629,7 +4642,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>379</v>
       </c>
@@ -4640,7 +4653,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>382</v>
       </c>
@@ -4651,7 +4664,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>385</v>
       </c>
@@ -4662,7 +4675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="51" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>386</v>
       </c>
@@ -4673,7 +4686,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>389</v>
       </c>
@@ -4684,7 +4697,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>392</v>
       </c>
@@ -4695,7 +4708,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>395</v>
       </c>
@@ -4706,7 +4719,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>398</v>
       </c>
@@ -4717,7 +4730,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>401</v>
       </c>
@@ -4728,7 +4741,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>404</v>
       </c>
@@ -4739,7 +4752,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>407</v>
       </c>
@@ -4750,7 +4763,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>410</v>
       </c>
@@ -4761,7 +4774,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>413</v>
       </c>
@@ -4772,7 +4785,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>416</v>
       </c>
@@ -4783,7 +4796,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>419</v>
       </c>
@@ -4794,7 +4807,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>422</v>
       </c>
@@ -4805,7 +4818,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>425</v>
       </c>
@@ -4816,7 +4829,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>428</v>
       </c>
@@ -4827,7 +4840,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>431</v>
       </c>
@@ -4838,7 +4851,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>434</v>
       </c>
@@ -4849,7 +4862,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>437</v>
       </c>
@@ -4860,7 +4873,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>440</v>
       </c>
@@ -4871,7 +4884,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>443</v>
       </c>
@@ -4882,7 +4895,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>446</v>
       </c>
@@ -4893,7 +4906,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>449</v>
       </c>
@@ -4904,7 +4917,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>452</v>
       </c>
@@ -4915,7 +4928,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>455</v>
       </c>
@@ -4926,7 +4939,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>458</v>
       </c>
@@ -4937,7 +4950,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>461</v>
       </c>
@@ -4948,7 +4961,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>464</v>
       </c>
@@ -4959,7 +4972,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>467</v>
       </c>
@@ -4970,7 +4983,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>470</v>
       </c>
@@ -4981,7 +4994,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>473</v>
       </c>
@@ -4992,7 +5005,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>476</v>
       </c>
@@ -5003,7 +5016,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>479</v>
       </c>
@@ -5014,7 +5027,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>482</v>
       </c>
@@ -5025,7 +5038,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>485</v>
       </c>
@@ -5036,7 +5049,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>488</v>
       </c>
@@ -5047,7 +5060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>489</v>
       </c>
@@ -5058,7 +5071,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>490</v>
       </c>
@@ -5069,7 +5082,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>491</v>
       </c>
@@ -5080,7 +5093,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>492</v>
       </c>
@@ -5091,7 +5104,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>493</v>
       </c>
@@ -5102,7 +5115,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>496</v>
       </c>
@@ -5113,7 +5126,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>499</v>
       </c>
@@ -5124,7 +5137,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>502</v>
       </c>
@@ -5135,7 +5148,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>505</v>
       </c>
@@ -5146,7 +5159,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>508</v>
       </c>
@@ -5157,7 +5170,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>511</v>
       </c>
@@ -5168,7 +5181,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>514</v>
       </c>
@@ -5179,7 +5192,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>517</v>
       </c>
@@ -5190,7 +5203,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>520</v>
       </c>
@@ -5201,7 +5214,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>523</v>
       </c>
@@ -5212,7 +5225,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>526</v>
       </c>
@@ -5223,7 +5236,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>529</v>
       </c>
@@ -5234,7 +5247,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>532</v>
       </c>
@@ -5245,7 +5258,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>535</v>
       </c>
@@ -5256,7 +5269,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
         <v>538</v>
       </c>
@@ -5267,7 +5280,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>541</v>
       </c>
@@ -5278,7 +5291,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>544</v>
       </c>
@@ -5289,7 +5302,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>547</v>
       </c>
@@ -5300,7 +5313,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
         <v>550</v>
       </c>
@@ -5311,7 +5324,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>553</v>
       </c>
@@ -5322,7 +5335,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
         <v>556</v>
       </c>
@@ -5333,7 +5346,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>559</v>
       </c>
@@ -5344,7 +5357,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>560</v>
       </c>
@@ -5355,7 +5368,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>561</v>
       </c>
@@ -5366,7 +5379,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>564</v>
       </c>
@@ -5377,7 +5390,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>567</v>
       </c>
@@ -5388,7 +5401,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
         <v>570</v>
       </c>
@@ -5399,7 +5412,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>573</v>
       </c>
@@ -5410,7 +5423,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>576</v>
       </c>
@@ -5421,7 +5434,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>579</v>
       </c>
@@ -5432,7 +5445,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
         <v>582</v>
       </c>
@@ -5443,7 +5456,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>585</v>
       </c>
@@ -5454,7 +5467,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>588</v>
       </c>
@@ -5465,7 +5478,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>590</v>
       </c>
@@ -5476,7 +5489,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
         <v>592</v>
       </c>
@@ -5487,7 +5500,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>595</v>
       </c>
@@ -5498,7 +5511,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
         <v>597</v>
       </c>
@@ -5509,7 +5522,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>599</v>
       </c>
@@ -5520,7 +5533,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
         <v>602</v>
       </c>
@@ -5531,7 +5544,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>605</v>
       </c>
@@ -5542,7 +5555,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
         <v>608</v>
       </c>
@@ -5553,7 +5566,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>611</v>
       </c>
@@ -5564,7 +5577,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
         <v>614</v>
       </c>
@@ -5575,7 +5588,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>617</v>
       </c>
@@ -5586,7 +5599,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>620</v>
       </c>
@@ -5597,7 +5610,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>623</v>
       </c>
@@ -5608,7 +5621,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>626</v>
       </c>
@@ -5619,7 +5632,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>629</v>
       </c>
@@ -5630,7 +5643,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
         <v>632</v>
       </c>
@@ -5641,7 +5654,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>635</v>
       </c>
@@ -5652,7 +5665,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="122.4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" ht="168.75" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>638</v>
       </c>
@@ -5663,7 +5676,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>641</v>
       </c>
@@ -5674,7 +5687,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
         <v>644</v>
       </c>
@@ -5685,7 +5698,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>647</v>
       </c>
@@ -5696,7 +5709,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
         <v>650</v>
       </c>
@@ -5707,7 +5720,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>653</v>
       </c>
@@ -5718,7 +5731,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>656</v>
       </c>
@@ -5729,7 +5742,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>659</v>
       </c>
@@ -5740,7 +5753,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
         <v>662</v>
       </c>
@@ -5751,7 +5764,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>665</v>
       </c>
@@ -5762,7 +5775,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
         <v>668</v>
       </c>
@@ -5773,7 +5786,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>671</v>
       </c>
@@ -5784,7 +5797,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
         <v>674</v>
       </c>
@@ -5795,7 +5808,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>677</v>
       </c>
@@ -5806,7 +5819,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" ht="348.75" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
         <v>680</v>
       </c>
@@ -5817,7 +5830,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="112.2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" ht="146.25" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>683</v>
       </c>
@@ -5828,7 +5841,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="295.8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
         <v>686</v>
       </c>
@@ -5839,7 +5852,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>689</v>
       </c>
@@ -5850,7 +5863,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="102" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" ht="146.25" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
         <v>692</v>
       </c>
@@ -5861,7 +5874,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>695</v>
       </c>
@@ -5872,7 +5885,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
         <v>698</v>
       </c>
@@ -5883,7 +5896,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>701</v>
       </c>
@@ -5894,7 +5907,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
         <v>704</v>
       </c>
@@ -5905,7 +5918,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>707</v>
       </c>
@@ -5916,7 +5929,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
         <v>710</v>
       </c>
@@ -5927,7 +5940,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>713</v>
       </c>
@@ -5938,7 +5951,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
         <v>716</v>
       </c>
@@ -5949,7 +5962,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>719</v>
       </c>
@@ -5960,7 +5973,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
         <v>722</v>
       </c>
@@ -5971,7 +5984,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="51" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>725</v>
       </c>
@@ -5982,7 +5995,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
         <v>728</v>
       </c>
@@ -5993,7 +6006,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>731</v>
       </c>
@@ -6004,7 +6017,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
         <v>734</v>
       </c>
@@ -6015,7 +6028,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="132.6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" ht="180" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>737</v>
       </c>
@@ -6026,7 +6039,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="71.400000000000006" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
         <v>740</v>
       </c>
@@ -6037,7 +6050,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>743</v>
       </c>
@@ -6048,7 +6061,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
         <v>746</v>
       </c>
@@ -6059,7 +6072,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>749</v>
       </c>
@@ -6070,7 +6083,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
         <v>752</v>
       </c>
@@ -6081,7 +6094,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>755</v>
       </c>
@@ -6092,7 +6105,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="51" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
         <v>758</v>
       </c>
@@ -6103,7 +6116,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>761</v>
       </c>
@@ -6114,7 +6127,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="102" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" ht="146.25" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
         <v>764</v>
       </c>
@@ -6125,7 +6138,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>767</v>
       </c>
@@ -6136,7 +6149,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
         <v>770</v>
       </c>
@@ -6147,7 +6160,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>773</v>
       </c>
@@ -6158,7 +6171,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
         <v>776</v>
       </c>
@@ -6169,7 +6182,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>779</v>
       </c>
@@ -6180,7 +6193,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
         <v>782</v>
       </c>
@@ -6191,7 +6204,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>785</v>
       </c>
@@ -6202,7 +6215,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
         <v>788</v>
       </c>
@@ -6213,7 +6226,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>791</v>
       </c>
@@ -6224,7 +6237,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="71.400000000000006" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
         <v>794</v>
       </c>
@@ -6235,7 +6248,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>797</v>
       </c>
@@ -6246,7 +6259,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
         <v>800</v>
       </c>
@@ -6257,7 +6270,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>803</v>
       </c>
@@ -6268,7 +6281,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
         <v>806</v>
       </c>
@@ -6279,7 +6292,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>809</v>
       </c>
@@ -6290,7 +6303,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
         <v>812</v>
       </c>
@@ -6301,7 +6314,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>815</v>
       </c>
@@ -6312,7 +6325,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
         <v>818</v>
       </c>
@@ -6323,7 +6336,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>821</v>
       </c>
@@ -6334,7 +6347,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
         <v>824</v>
       </c>
@@ -6345,7 +6358,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>827</v>
       </c>
@@ -6356,7 +6369,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
         <v>830</v>
       </c>
@@ -6367,7 +6380,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>833</v>
       </c>
@@ -6378,7 +6391,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
         <v>836</v>
       </c>
@@ -6389,7 +6402,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>839</v>
       </c>
@@ -6400,7 +6413,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
         <v>842</v>
       </c>
@@ -6411,7 +6424,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>845</v>
       </c>
@@ -6422,7 +6435,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
         <v>848</v>
       </c>
@@ -6433,7 +6446,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>851</v>
       </c>
@@ -6444,7 +6457,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
         <v>854</v>
       </c>
@@ -6455,7 +6468,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>857</v>
       </c>
@@ -6466,7 +6479,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
         <v>860</v>
       </c>
@@ -6477,7 +6490,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>863</v>
       </c>
@@ -6488,7 +6501,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
         <v>866</v>
       </c>
@@ -6499,7 +6512,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
         <v>869</v>
       </c>
@@ -6515,6 +6528,6 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" orientation="portrait"/>
+  <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/extra/IHME_GBD_2023_COD_CAUSE_ICD_CODE_MAP_Y2025M10D12.XLSX
+++ b/extra/IHME_GBD_2023_COD_CAUSE_ICD_CODE_MAP_Y2025M10D12.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DATA\recod_GC\extra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F20FD6-795C-4933-8C98-7C230B7434D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE14E99-4756-44C6-8A39-E10D405D67BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$2</definedName>
   </definedNames>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -46,9 +46,6 @@
     <t>HIV/AIDS and sexually transmitted infections</t>
   </si>
   <si>
-    <t>A50-A58, A60-A60.9, A63-A63.8, B20-B24.9, B63, F02.4, I98.0, K67.0-K67.2, M03.1, M73.0-M73.1</t>
-  </si>
-  <si>
     <t>042-044.9, 054.1, 090-099.9</t>
   </si>
   <si>
@@ -127,9 +124,6 @@
     <t>Respiratory infections and tuberculosis</t>
   </si>
   <si>
-    <t>A10-A14, A15-A19.9, A48.1, A70, B34.2, B90-B90.9, B97.2, B97.4-B97.6, H70-H70.9, J00-J02.8, J03-J03.8, J04-J04.2, J05-J05.1, J06.0-J06.8, J09-J15.8, J16-J16.9, J20-J21.9, J36-J36.0, J91.0, K23.0, K67.3, K93.0, M49.0, N74.0-N74.1, P23.0-P23.4, P37.0, U04-U04.9, U07-U07.2, U84.3</t>
-  </si>
-  <si>
     <t>010-019.9, 034.0, 079.6, 137-137.9, 138.0-138.9, 320.4, 381-383.9, 460-464.4, 464.8-464.9, 465.0-465.8, 466-469, 475-475.9, 476.9, 480-482.8, 483.0-483.9, 484.1-484.2, 484.6-484.7, 487-489, 730.4-730.6, 770.0</t>
   </si>
   <si>
@@ -241,9 +235,6 @@
     <t>Enteric infections</t>
   </si>
   <si>
-    <t>A00-A00.9, A01.0-A06.3, A06.9-A09.9, A80-A80.9, B91, G14-G14.6, K52.1-K52.3, M89.6, R19.7</t>
-  </si>
-  <si>
     <t>001-001.9, 002.0-006.2, 006.9-009.9, 045-045.9, 138, 558.2-558.9, 730.7, 979.5</t>
   </si>
   <si>
@@ -448,9 +439,6 @@
     <t>Other infectious diseases</t>
   </si>
   <si>
-    <t>A06.4-A06.8, A20-A28.9, A32-A39.9, A48.2, A48.4-A48.5, A65-A65.0, A69-A69.2, A74, A74.8-A74.9, A77.4, A81-A81.9, A83-A89.9, B00-B06.9, B10-B10.8, B15-B16.2, B17.0, B17.2, B19.1, B25-B27.9, B29.4, B33-B33.1, B33.3-B33.8, B47-B48.8, B94.1, B95-B95.5, D70.3, D89.3, F02.1, F07.1, G00.0-G00.8, G03-G03.8, G04-G05.1, G05.3-G05.8, G21.3, I00, I02, I02.9, K67.8, K75.3, K76.3, K77.0, M49.1, P35-P35.3, P35.8-P35.9, P37, P37.1, P37.5-P37.9, U82-U84, U85-U89.9, Z16-Z16.3</t>
-  </si>
-  <si>
     <t>006.3-006.8, 020-029, 032-034, 034.1-034.9, 036-037.9, 040, 040.1-041.0, 046-054.0, 054.2-059.9, 062-064.9, 070.0-070.2, 072-074.1, 074.3-075.9, 078.3-078.7, 079-079.5, 079.7, 082.4, 100-101.6, 104-104.9, 136-136.2, 139-139.0, 320.0-320.3, 320.5-320.8, 321-323.9, 390-390.9, 392, 392.9, 484.0, 484.3-484.5, 771.0-771.3, V09-V09.9</t>
   </si>
   <si>
@@ -565,9 +553,6 @@
     <t>Maternal and neonatal disorders</t>
   </si>
   <si>
-    <t>C58-C58.0, N96, N98-N98.9, O00-O07.9, O09-O16.9, O20-O26.9, O28-O36.9, O40-O48.1, O60-O77.9, O80-O92.7, O96-O98.6, O98.8-P04, P04.2, P04.5-P05.9, P07-P08.2, P10-P15.9, P20-P22.9, P24-P29.9, P36-P36.9, P37.2, P38-P39.9, P50-P61.9, P70-P70.1, P70.4-P72.0, P72.2-P72.9, P76-P78.9, P83-P84, P90-P91.9, P94, P94.1-P94.9, P96, P96.3, P96.8</t>
-  </si>
-  <si>
     <t>181-181.9, 630-636.9, 638-638.9, 640-679.1, 760-760.6, 760.8-763.4, 763.6-768, 768.2-770, 770.1-771, 771.4-774.9, 775.0, 776-779.2</t>
   </si>
   <si>
@@ -754,9 +739,6 @@
     <t>Neoplasms</t>
   </si>
   <si>
-    <t>C00-C13.9, C15-C22.8, C23-C25.9, C30-C34.9, C37-C38.8, C40-C41.9, C43-C45.9, C47-C54.9, C56-C57.8, C60-C63.8, C64-C67.9, C68.0-C68.8, C69.0-C69.8, C70-C73.9, C75-C75.8, C81-C82.9, C83.0-C83.8, C84-C85.0, C85.2-C85.8, C86-C86.6, C88-C91.0, C91.2-C91.3, C91.6, C92-C92.6, C93-C93.1, C93.3, C93.8, C94-C94.5, C94.7-C96.9, D00.1-D00.2, D01.0-D01.3, D02.0-D02.3, D03-D06.9, D07.0-D07.2, D07.4-D07.5, D09.0, D09.2-D09.3, D09.8, D10.0-D10.7, D11-D12.9, D13.0-D13.7, D14.0-D14.3, D15-D16.9, D22-D24.9, D26.0-D27.9, D28.0-D28.1, D28.7, D29.0-D29.8, D30.0-D30.8, D31-D36, D36.1-D36.7, D37.1-D37.5, D38.0-D38.5, D39.1-D39.2, D39.8, D40.0-D40.8, D41.0-D41.8, D42-D43.9, D44.0-D44.8, D45-D47.9, D48.0-D48.6, D49.2-D49.4, D49.6</t>
-  </si>
-  <si>
     <t>140-148.9, 150-155.1, 155.3-158.9, 160-164.9, 170-175.9, 180-180.9, 182-183.8, 184.0-184.4, 184.8, 185-186.9, 187.1-187.8, 188-188.9, 189.0-189.8, 190-190.8, 191-193.9, 194.1-194.8, 200-202.8, 203-204.0, 204.2, 205-205.3, 206-206.1, 207-208.9, 209.0-209.1, 209.4-209.5, 210.0-210.9, 211.0-211.8, 212.0-212.8, 213-213.9, 217-217.8, 219.0, 220-220.9, 221.0-221.8, 222.0-222.8, 223.0-223.8, 224-228.9, 229.0, 229.8, 230.1-230.8, 231.0-231.2, 232-232.9, 233.0-233.2, 233.4-233.5, 233.7, 234.0-234.8, 235.0, 235.4, 235.6-235.8, 236.1-236.2, 236.4-236.5, 236.7, 237.0-237.1, 237.3, 237.5-237.9, 238.0-238.9, 239.2-239.4, 239.6, 569.0, 610-610.9, 622.7</t>
   </si>
   <si>
@@ -1186,9 +1168,6 @@
     <t>Cardiovascular diseases</t>
   </si>
   <si>
-    <t>B33.2, G45-G46.8, I01-I01.9, I02.0, I05-I09.9, I11-I11.9, I20-I25.9, I27.0, I27.2, I28-I28.9, I30-I31.1, I31.8-I37.8, I38-I41.1, I41.8-I41.9, I42.1-I42.8, I43-I43.9, I47-I48.9, I51.0-I51.4, I60-I63.9, I65-I66.9, I67.0-I67.3, I67.5-I67.6, I68.0-I68.2, I69.0-I69.3, I70.2-I70.7, I71-I73.9, I77-I83.9, I86-I89.0, I89.9, I98, K75.1</t>
-  </si>
-  <si>
     <t>074.2, 391-391.9, 392.0, 393-398.9, 402-402.9, 410-414.9, 416.0, 417-417.9, 420-423, 423.1-423.9, 424.0-424.3, 424.8, 425.0-425.5, 425.7-425.8, 427.0-427.3, 427.6-427.8, 429.0, 430-435.9, 437.0-437.2, 437.5-437.8, 440.2, 440.4, 441-443.9, 447-454.9, 456, 456.3-457, 457.1, 457.8-457.9, 459, 459.1-459.3</t>
   </si>
   <si>
@@ -1384,9 +1363,6 @@
     <t>Chronic respiratory diseases</t>
   </si>
   <si>
-    <t>D86-D86.2, D86.9, G47.3, J30-J35.9, J37-J39.9, J41-J46.9, J60-J63.8, J66-J68.9, J70, J70.8-J70.9, J82, J84-J84.9, J91, J91.8-J92.9</t>
-  </si>
-  <si>
     <t>135-135.9, 327.2-327.8, 470-474.9, 476-476.1, 477-479, 491-493.9, 495-504.9, 506-506.9, 508-509, 515, 516-517.8, 518.6, 518.9, 519.1-519.4</t>
   </si>
   <si>
@@ -1474,9 +1450,6 @@
     <t>Digestive diseases</t>
   </si>
   <si>
-    <t>B18-B18.9, I84-I85.9, I98.2, K20-K20.9, K22-K22.6, K22.8-K23, K23.8-K29.9, K31-K31.8, K35-K38.9, K40-K42.9, K44-K46.9, K50-K52, K52.8-K52.9, K55-K62.6, K62.8-K62.9, K63.5, K64-K64.9, K66.8, K67, K68, K70-K70.3, K71.7, K73-K75, K75.2, K75.4-K76.2, K76.4-K77, K77.8, K80-K83.9, K85-K87.1, K90-K90.9, K92.8, K93.8, M07.4-M07.5, M09.1-M09.2</t>
-  </si>
-  <si>
     <t>455-455.9, 456.0-456.2, 530-530.0, 530.2-530.6, 531-536.1, 537-537.6, 537.8, 538, 540-543.9, 550-551.1, 551.3-552.1, 552.3-553.1, 553.3-558.0, 560-560.3, 560.8-560.9, 562-562.1, 564-564.1, 564.5-564.7, 565-566.9, 569.1-569.5, 569.7, 571-571.9, 572.2-573.0, 573.4-577.9, 579-579.2, 579.4-579.9</t>
   </si>
   <si>
@@ -1633,9 +1606,6 @@
     <t>Neurological disorders</t>
   </si>
   <si>
-    <t>F00-F02.0, F02.2-F02.3, F02.8-F03.9, G10-G13.8, G20-G20.9, G23-G24, G24.1-G25.0, G25.2-G25.3, G25.5, G25.8-G26.0, G30-G31.1, G31.8-G31.9, G35-G37.9, G40-G41.9, G61-G61.9, G70-G71.1, G71.3-G72, G72.2-G73.7, G90-G90.9, G95-G95.9, M33-M33.9, P94.0</t>
-  </si>
-  <si>
     <t>290-290.9, 294.1-294.9, 330-331.2, 331.5-332.0, 333-337.9, 340-341.9, 345-345.9, 349, 349.2-349.8, 353.8-353.9, 356-356.9, 357.0-357.1, 357.3-357.4, 357.7, 358-359.9, 775.2</t>
   </si>
   <si>
@@ -1861,9 +1831,6 @@
     <t>Skin and subcutaneous diseases</t>
   </si>
   <si>
-    <t>A46-A46.0, A66-A67.9, B86, D86.3, H05.0-H05.1, I89.1-I89.8, L00-L05.9, L08-L08.9, L10-L14.0, L51-L51.9, L88-L89.9, L97-L98.4, M07.0-M07.3, M09.0, M72.5-M72.6</t>
-  </si>
-  <si>
     <t>035-035.9, 102-103.9, 133-133.6, 376.0-376.1, 457.2-457.3, 680-689, 694-695.3, 707-707.9</t>
   </si>
   <si>
@@ -1915,9 +1882,6 @@
     <t>Musculoskeletal disorders</t>
   </si>
   <si>
-    <t>I27.1, I67.7, L93-L93.2, M00-M03.0, M03.2-M03.6, M05-M07, M07.6-M09, M09.8, M30-M32.9, M34-M36.8, M40-M43.1, M65-M65.0, M71.0-M71.1, M80-M82.8, M86.3-M86.4, M87-M87.0, M88-M89.0, M89.5, M89.7-M89.9</t>
-  </si>
-  <si>
     <t>416.1, 437.4, 446-446.9, 695.4-695.5, 710-711.9, 714-714.3, 714.8-714.9, 730.1, 732-732.9, 733.0-733.1</t>
   </si>
   <si>
@@ -1942,9 +1906,6 @@
     <t>Other non-communicable diseases</t>
   </si>
   <si>
-    <t>D25-D26, D28.2, D55-D59, D59.1, D59.3-D59.5, D59.8-D61.9, D64.0, D66-D67, D68.0-D69.4, D69.6-D69.8, D70-D70.0, D70.4-D75.8, D76-D77, D86.8, D89-D89.2, E03-E03.1, E03.3-E06.3, E06.5-E07.1, E16.1-E16.9, E20-E23.0, E23.2-E24.1, E24.3, E24.8-E27.2, E27.4-E34, E34.1-E34.8, E65-E66.0, E66.2-E68, E70-E85.2, E88-E88.2, E88.4-E88.9, G71.2, N10-N12.9, N13.6, N15, N15.1-N16.8, N20-N23.0, N25-N28.1, N29-N30.3, N30.8-N32.0, N32.3-N32.4, N34-N34.3, N36-N36.9, N39-N39.2, N41-N41.9, N44-N44.0, N45-N45.9, N49-N49.9, N60-N60.9, N72-N72.0, N75-N77.8, N80-N81.9, N83-N83.9, N84.0-N84.1, N87-N87.9, P72.1, P96.0, Q00-Q07.9, Q10.4-Q18.9, Q20-Q28.9, Q30-Q45.9, Q50-Q56.4, Q60-Q86, Q86.8-Q87.8, Q89-Q89.8, Q90-Q93.9, Q95-Q99.8, R95-R95.9</t>
-  </si>
-  <si>
     <t>218-219, 219.1-219.9, 236.0, 240-243.9, 245-246.9, 251-251.2, 251.4-253.6, 253.8-259.1, 259.3-259.9, 270-273.9, 275-276, 277-277.2, 277.4-277.9, 278.0-278.8, 282-284.9, 286-286.5, 286.7-289.0, 289.4-289.7, 588-588.9, 590-590.9, 592-593.8, 594-598.1, 598.8-599.6, 599.8, 601-602.9, 604-604.9, 608.2, 615-618.9, 620-620.9, 621.0, 621.4-621.9, 622.1-622.6, 629-629.8, 740-758.9, 759.0-759.8, 775.3, 788.0, 798-798.0</t>
   </si>
   <si>
@@ -2068,27 +2029,18 @@
     <t>Garbage Code (GBD Level 1)</t>
   </si>
   <si>
-    <t>A40-A41.9, A48.0, A48.3, A49.0-A49.1, A59-A59.9, A71-A71.9, A74.0, B07-B07.9, B30-B30.9, B35-B36.9, B85-B85.4, B87-B88.9, B94.0, D50-D50.0, D50.9, D62-D63.0, D63.8-D64, D64.1-D65.9, D68, D69.9, E15-E16, E50-E50.9, E64.1, E85.3-E87.6, E87.8-E87.9, F19-F19.9, G06-G08.0, G32-G32.8, G43-G44.2, G44.4-G44.8, G47-G47.2, G47.4-G47.9, G50-G60.9, G62-G62.0, G62.2-G65.2, G80-G83.9, G89-G89.4, G91-G91.2, G91.4-G93, G93.1-G93.2, G93.4-G93.6, G94.0-G94.8, G99-H05, H05.2-H69.9, H71-H99, I26-I26.9, I31.2-I31.4, I46-I46.9, I50.0-I50.4, I76, I91-I91.1, I95-I95.1, I95.8-I95.9, J69-J69.9, J80-J80.9, J81.0, J85-J85.3, J86-J86.9, J90-J90.0, J93-J93.1, J93.8-J94.9, J96-J96.9, J98.1-J98.3, K00-K19, K30, K65-K66.1, K66.9, K68.1-K68.9, K71-K71.6, K71.8-K72.9, K75.0, L20-L30.9, L40-L50.9, L52-L54.8, L56-L56.2, L56.4-L56.5, L57-L57.9, L59-L68.9, L70-L76.8, L80-L87.9, L90-L92.9, L94-L96, L98.5-L99.8, M04, M10-M12.0, M12.2-M29, M37-M39, M43.2-M49, M49.2-M64, M65.1-M71, M71.2-M72.4, M72.8-M73, M73.8-M79.9, M83-M86.2, M86.5-M86.9, M87.2-M87.9, M89.1-M89.4, M90-M99.9, N17-N17.9, N19-N19.9, N32.1-N32.2, N32.8-N33.8, N35-N35.9, N37-N37.8, N39.3-N39.8, N42-N43.4, N44.1-N44.8, N46-N48.9, N50-N53.9, N61-N64.9, N82-N82.9, N91-N91.5, N95, N95.1-N95.9, N97-N97.9, R02-R02.9, R03.1-R04, R04.1-R04.9, R07.0, R08-R12.0, R14-R19.6, R19.8-R23, R23.1-R30.9, R32-R50.1, R50.8-R57.9, R58.0-R72.9, R74-R78, R78.6-R94.8, R96-R99.9, U05, U08-U49, U51-U81, U90-U99, X40-X44.9, X46-X46.9, X49-X49.9, Y10-Y14.9, Y16-Y19.9, Z00-Z15.8, Z17-unsp.</t>
-  </si>
-  <si>
     <t>038-038.9, 040.0, 041.1, 076-078.2, 110-111.9, 125-125.3, 126-126.9, 127.3-127.9, 131-132.9, 133.8-134.9, 136.6, 139.1, 139.9, 247-248, 264-264.9, 274-274.9, 276.0-276.9, 277.3, 280-281, 285-285.9, 286.6, 289.1-289.3, 293, 294-294.0, 305, 305.9, 324-327.1, 328-329, 338-339.1, 339.3-339.8, 342-344.9, 346-346.9, 350-353.6, 354-355.9, 360-362, 362.1-376, 376.2-380.9, 384-389.9, 415-415.9, 423.0, 424, 424.4-424.5, 424.9, 427.5, 427.9-428.9, 437.3, 458-458.9, 459.0, 507-507.9, 510-513.9, 518.1-518.3, 520-529.9, 536.3, 536.8-536.9, 537.7, 537.9, 564.8-564.9, 567-568.9, 570-570.9, 572-572.1, 573.1-573.3, 584-584.9, 586-587.9, 603-603.9, 605-608.1, 608.3-609, 611-612.1, 619-619.9, 621, 621.1-621.3, 622-622.0, 622.8-623.6, 623.8-624.5, 624.8-628.9, 629.9, 690-693.9, 695.8-706.9, 708-709.9, 712-713.8, 715-716, 716.2-721.6, 721.8-730.0, 730.2-730.3, 730.8-731.9, 733, 733.2-734.2, 737-738, 738.2-739.9, 780-782.4, 782.6-784.6, 784.9, 785.4-786, 786.6, 786.8, 787, 787.3-788, 788.3-790.1, 790.4-796.1, 796.3-797.9, 798.1-799.9, E850.3, E850.4, E850.5, E850.6, E850.7, E850.8, E850.9, E851-E851.0, E852-E852.0, E852.1, E852.2, E852.3, E852.4, E852.5, E852.8, E852.9, E853-E853.0, E853.1, E853.2, E853.8, E853.9, E854-E854.0, E854.1, E854.2, E854.3, E854.8-E855.0, E855.1, E855.2, E855.3, E855.4, E855.5, E855.6, E855.8, E855.9, E858-E858.0, E858.1, E858.2, E858.3, E858.4, E858.5, E858.6, E858.7, E858.8, E858.9, E866-E866.0, E866.1, E866.2, E866.3, E866.4, E866.5, E866.6, E866.7, E866.8, E866.9, E980-E982.9, V01-V08, V10-uns</t>
   </si>
   <si>
     <t>Garbage Code (GBD Level 2)</t>
   </si>
   <si>
-    <t>A14.9, A29-A30.9, A45-A45.9, A47-A48, A48.8-A49, A49.3-A49.9, A61-A62, A72-A73, A76, A97, B08-B09, B11-B14, B28-B29, B31-B32.4, B34-B34.1, B34.3-B34.9, B61-B62, B68-B68.9, B73-B74.2, B76-B76.9, B79-B81.8, B84, B92-B94, B94.8-B94.9, B95.6-B97.1, B97.3, B97.7-B99.9, F07.2, F17-F17.9, G44.3, G91.3, G93.0, G93.3, I10-I10.9, I15-I15.9, I27, I27.8-I27.9, I50, I50.8-I50.9, I67.4, I70-I70.1, I70.8-I70.9, I74-I75.8, J81, J81.1, K92.0-K92.2, N70-N71.9, N73-N74, N74.2-N74.8, R03-R03.0, R04.0, R05-R06.9, R13-R13.9, R23.0, R58, S00-T99.9, U50, W47-W48, W63, W71-W72, W82, W95-W97, W98, X07, X55-X56, X59-X59.9, Y20-Y34.9, Y86-Y87, Y87.2, Y89, Y89.9, Y92-Y99.9</t>
-  </si>
-  <si>
     <t>000-000.9, 030-030.9, 041.2-041.9, 067-069, 078.8-078.9, 079.8-079.9, 089-089.9, 105-109.9, 119, 136.8-136.9, 139.8, 304, 304.9, 305.1, 339.2, 401-401.9, 405-405.9, 416, 416.2-416.9, 440-440.1, 440.3, 440.8-440.9, 444-445.8, 490-490.9, 494-494.9, 514-514.9, 515.0-515.9, 518-518.0, 518.4-518.5, 518.8, 536.2, 578-578.9, 599.7, 613-614.9, 714.4, 716.1, 721.7, 735-736.9, 738.0-738.1, 784.7-784.8, 786.3, 787.0-787.2, 796.2, 800-979.4, 979.6-E80, E83, E839, E85, E859, E87, E877, E88, E887-E887.0, E928.9, E929, E929.8-E929.9, E983-E985.7, E988-E989</t>
   </si>
   <si>
     <t>Garbage Code (GBD Level 3)</t>
   </si>
   <si>
-    <t>A01, A31-A31.9, A42-A44.9, A49.2, A64-A64.0, A99-A99.0, B17, B17.1, B17.8-B17.9, B19-B19.0, B19.2-B19.9, B37-B46.9, B49-B49.9, B55, B55.1-B55.9, B58-B59.9, B89, B94.2, C14-C14.9, C22.9, C26-C29, C35-C36, C39-C39.9, C42, C46-C46.9, C55-C55.9, C57.9, C59, C63.9, C68, C68.9, C74-C74.9, C75.9-C80.9, C83, C83.9, C85.1, C85.9, C87, C94.6, C97-D00.0, D01, D01.4-D02, D02.4-D02.9, D07, D07.3, D07.6-D09, D09.1, D09.7, D09.9-D10, D10.9, D13, D13.9-D14, D14.4, D17-D21.9, D28, D28.9-D29, D29.9-D30, D30.9, D36.0, D36.9-D37.0, D37.6-D38, D38.6-D39.0, D39.7, D39.9-D40, D40.9-D41, D41.9, D44, D44.9, D48, D48.7-D49.1, D49.5, D49.7-D49.9, D54, D75.9, D79-D85, D87-D88, D89.8-D99, E07.8-E08.9, E17-E19, E34.0, E34.9-E35.8, E37-E39, E47-E49., E62, E69, E87.7, E90-E998, F04-F07.0, F07.8-F09.9, F20-F50, F50.8-F99.0, G09-G09.9, G15-G19, G21, G21.2, G21.4-G22.0, G27-G29, G33-G34, G38-G39., G42, G48-G49, G66-G69, G74-G79, G84-G88, G93.8-G94, G96-G96.9, G98-G98.9, I00.0, I03-I04., I14-I14., I16-I19, I29-I29.9, I44-I45.9, I49-I49.9, I51, I51.6-I59, I90, I91.9-I94, I96-I96.9, I98.4-I98.8, I99-ID5.9, J02.9, J03.9, J04.3, J06, J06.9, J40-J40.9, J47-J59, J65-J65.0, J71-J79, J81.9, J83, J85.9, J87-J89, J90.9, J93.6, J97-J98.0, J98.4-J99.8, K21-K21.9, K22.7, K31.9-K34, K39, K47-K49, K53-K54, K63-K63.4, K63.8-K63.9, K69, K70.4-K70.9, K78-K79, K84, K88-K89, K92, K92.9-K93, K96-K99, L06-L07, L09, L15-L19, L31-L39, L69, L77-L79, N09, N13-N13.5, N13.7-N13.9, N24, N28.8-N28.9, N38, N39.9-N40.9, N54-N59, N66-N69, N78-N79, N84, N84.2-N86, N88-N90.9, N92-N94.9, N95.0, O08-O08.9, O17-O19, O27, O37-O39, O49-O59, O78-O79, O93-O95.9, P06, P09, P16-P19.9, P30-P34.2, P40-P49, P62-P69, P73-P75.0, P79-P82, P85-P89, P92-P92.9, P96.9-P99.9, Q08-Q10.3, Q19, Q29-Q29., Q46-Q49, Q57, Q88, Q89.9, Q94, Q99.9-R01.2, R07, R07.1-R07.9, R31-R31.9, X64-X64.9, X69-X69.9</t>
-  </si>
-  <si>
     <t>002, 031-031.9, 039-039.9, 070, 070.4-070.9, 085, 085.1-085.9, 088.0-088.7, 112-118.9, 130-130.9, 136.3-136.5, 149-149.9, 155.2, 159-159.9, 165-169, 176-179.9, 183.9-184, 184.5, 184.9, 187, 187.9, 189, 189.9, 190.9, 195-199.9, 202.9, 209, 209.2-209.3, 209.6-210, 211, 211.9-212, 212.9, 214-216.9, 221, 221.9-222, 222.9-223, 223.9, 229, 229.1, 229.9-230.0, 230.9-231, 231.8-231.9, 233, 233.3, 233.6, 233.9-234, 234.9-235, 235.1-235.3, 235.5, 235.9-236, 236.3, 236.6, 236.9, 239-239.1, 239.5, 239.7-239.9, 249-249.9, 259.2, 278, 279-279.9, 293.0-293.9, 295-302.9, 306-307.0, 307.2-307.4, 307.6-319.9, 331.3-331.4, 332.1-332.9, 347-348.9, 349.9, 357, 357.8-357.9, 399-400.0, 406-409.4, 418-419.9, 426-427, 427.4, 429, 429.2-429.9, 459.5-459.9, 464.5, 465, 465.9, 505-505.9, 519, 519.8-519.9, 530.1, 530.7-530.9, 544-549, 559-559.0, 560.4-560.7, 561, 562.2-563, 569, 569.8-569.9, 591-591.9, 593.9, 599.9-600.9, 623.7, 624.6, 637-637.9, 639-639.9, 759, 759.9, 775, 775.4-775.9, 779.3, 779.7-779.9, 782.5, 785-785.3, 786.0-786.2, 786.4-786.5, 786.7, 786.9, 788.1-788.2, E950, E950.9, E958, E958.9-E959, E986-E987.9</t>
   </si>
   <si>
@@ -2104,9 +2056,6 @@
     <t>Garbage Code (GBD Level 4)</t>
   </si>
   <si>
-    <t>B16.9, B54-B54.0, B64, B82-B82.9, B83.9, C69, C69.9, C91.1, C91.4-C91.5, C91.7-C91.9, C92.7-C92.9, C93.2, C93.5-C93.7, C93.9, E12-E14.9, G00, G00.9-G02.1, G03.9, I37.9, I42-I42.0, I42.9, I51.5, I64-I64.9, I67, I67.8-I68, I68.8-I69, I69.4-I69.9, J07-J08, J15.9, J17-J19.6, J22-J29, J64-J64.9, P23, P23.5-P23.9, R73-R73.9, V87-V87.1, V87.4-V88.1, V88.4-V89.9, V99-V99.0, X84-X84.9, Y09-Y09.9, Y85-Y85.9</t>
-  </si>
-  <si>
     <t>070.3, 194-194.0, 194.9, 204.1, 204.5-204.9, 205.8-205.9, 206.2-206.9, 237, 237.2, 237.4, 238, 244, 244.9, 250-250.9, 289.8-289.9, 307.5, 320, 320.9, 357.2, 362.0, 425, 425.9, 429.1, 436-437, 437.9-439.6, 482.9-483, 484, 484.8-486.9, 790.2, E800.8-E800.9, E801.8-E801.9, E802.8-E802.9, E803.8-E803.9, E804.8-E804.9, E805.8-E805.9, E806.8-E806.9, E807.8-E810, E810.8-E811, E811.8-E812, E812.8-E813, E813.8-E814, E814.8-E815, E815.8-E816, E816.8-E817, E817.8-E818, E818.8-E819, E819.8-E820, E820.8-E821, E821.8-E822, E822.8-E823, E823.8-E824, E824.8-E825, E825.8-E826, E826.8-E827, E827.8-E828, E828.8-E829, E829.8-E829.9, E929.0</t>
   </si>
   <si>
@@ -2642,13 +2591,3883 @@
   </si>
   <si>
     <t>List of International Classification of Diseases (ICD) codes mapped to the Global Burden of Disease cause list for causes of death</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A50-A58, A60-A60.9, A63-A63.8, B20-B24.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>B63</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, F02.4, I98.0, K67.0-K67.2, M03.1, M73.0-M73.1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A10-A14</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, A15-A19.9, A48.1, A70, B34.2, B90-B90.9, B97.2, B97.4-B97.6, H70-H70.9, J00-J02.8, J03-J03.8, J04-J04.2, J05-J05.1, J06.0-J06.8, J09-J15.8, J16-J16.9, J20-J21.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J36-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J36.0, J91.0, K23.0, K67.3, K93.0, M49.0, N74.0-N74.1, P23.0-P23.4, P37.0, U04-U04.9, U07-U07.2, U84.3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A00-A00.9, A01.0-A06.3, A06.9-A09.9, A80-A80.9, B91, G14-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>G14.6</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, K52.1-K52.3, M89.6, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>R19.7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A06.4-A06.8, A20-A28.9, A32-A39.9, A48.2, A48.4-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A48.5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A65</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">-A65.0, A69-A69.2, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A74</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, A74.8-A74.9, A77.4, A81-A81.9, A83-A89.9, B00-B06.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>B10-B10.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, B15-B16.2, B17.0, B17.2, B19.1, B25-B27.9, B29.4, B33-B33.1, B33.3-B33.8, B47-B48.8, B94.1, B95-B95.5, D70.3, D89.3, F02.1, F07.1, G00.0-G00.8, G03-G03.8, G04-G05.1, G05.3-G05.8, G21.3,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> I00, I02</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, I02.9, K67.8, K75.3, K76.3, K77.0, M49.1, P35-P35.3, P35.8-P35.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>P37</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, P37.1, P37.5-P37.9, U82-U84, U85-U89.9, Z16-Z16.3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C58</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">-C58.0, N96, N98-N98.9, O00-O07.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O09-O16.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, O20-O26.9, O28-O36.9, O40-O48.1, O60-O77.9, O80-O92.7, O96-O98.6, O98.8-P04, P04.2, P04.5-P05.9, P07-P08.2, P10-P15.9, P20-P22.9, P24-P29.9, P36-P36.9, P37.2, P38-P39.9, P50-P61.9, P70-P70.1, P70.4-P72.0, P72.2-P72.9, P76-P78.9, P83-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>P84</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, P90-P91.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>P94</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, P94.1-P94.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>P96</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, P96.3, P96.8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C00-C13.9, C15-C22.8, C23-C25.9, C30-C34.9, C37-C38.8, C40-C41.9, C43-C45.9, C47-C54.9, C56-C57.8, C60-C63.8, C64-C67.9, C68.0-C68.8, C69.0-C69.8, C70-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C73.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, C75-C75.8, C81-C82.9, C83.0-C83.8, C84-C85.0, C85.2-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C85.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, C86-C86.6, C88-C91.0, C91.2-C91.3, C91.6, C92-C92.6, C93-C93.1, C93.3, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C93.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, C94-C94.5, C94.7-C96.9, D00.1-D00.2, D01.0-D01.3, D02.0-D02.3, D03-D06.9, D07.0-D07.2, D07.4-D07.5, D09.0, D09.2-D09.3, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D09.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D10.0-D10.7, D11-D12.9, D13.0-D13.7, D14.0-D14.3, D15-D16.9, D22-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D24.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D26.0-D27.9, D28.0-D28.1, D28.7, D29.0-D29.8, D30.0-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D30.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D31-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D36</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, D36.1-D36.7, D37.1-D37.5, D38.0-D38.5, D39.1-D39.2, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D39.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D40.0-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D40.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D41.0-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D41.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, D42-D43.9, D44.0-D44.8, D45-D47.9, D48.0-D48.6, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D49.2-D49.4, D49.6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B33.2, G45-G46.8, I01-I01.9, I02.0, I05-I09.9, I11-I11.9, I20-I25.9, I27.0, I27.2, I28-I28.9, I30-I31.1, I31.8-I37.8, I38-I41.1, I41.8-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I41.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, I42.1-I42.8, I43</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-I43.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, I47-I48.9, I51.0-I51.4, I60-I63.9, I65-I66.9, I67.0-I67.3, I67.5-I67.6, I68.0-I68.2, I69.0-I69.3, I70.2-I70.7, I71-I73.9, I77-I83.9, I86-I89.0, I89.9,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> I98</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, K75.1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>D86-D86.2, D86.9, G47.3, J30-J35.9, J37-J39.9, J41-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J46.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, J60-J63.8, J66-J68.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J70</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, J70.8-J70.9, J82, J84-J84.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J91, J91.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-J92.9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">B18-B18.9, I84-I85.9, I98.2, K20-K20.9, K22-K22.6, K22.8-K23, K23.8-K29.9, K31-K31.8, K35-K38.9, K40-K42.9, K44-K46.9, K50-K52, K52.8-K52.9, K55-K62.6, K62.8-K62.9, K63.5, K64-K64.9, K66.8, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>K67, K68</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, K70-K70.3, K71.7, K73</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-K75</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, K75.2, K75.4-K76.2, K76.4-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>K77</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, K77.8, K80-K83.9, K85-K87.1, K90-K90.9, K92.8, K93.8, M07.4-M07.5, M09.1-M09.2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>F00-F02.0, F02.2-F02.3, F02.8-F03.9, G10-G13.8, G20-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>G20.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, G23-G24, G24.1-G25.0, G25.2-G25.3, G25.5, G25.8-G26.0, G30-G31.1, G31.8-G31.9, G35-G37.9, G40-G41.9, G61-G61.9, G70-G71.1, G71.3-G72, G72.2-G73.7, G90-G90.9, G95-G95.9, M33-M33.9, P94.0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A46</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-A46.0, A66-A67.9, B86, D86.3, H05.0-H05.1, I89.1-I89.8, L00-L05.9, L08-L08.9, L10-L14.0, L51-L51.9, L88-L89.9, L97-L98.4, M07.0-M07.3, M09.0, M72.5-M72.6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>I27.1, I67.7, L93-L93.2, M00-M03.0, M03.2-M03.6, M05-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>M07</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, M07.6-M09, M09.8, M30-M32.9, M34-M36.8, M40-M43.1, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>M65</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-M65.0, M71.0-M71.1, M80-M82.8, M86.3-M86.4, M87-M87.0, M88-M89.0, M89.5, M89.7-M89.9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>D25-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D26</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D28.2, D55-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D59</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D59.1, D59.3-D59.5, D59.8-D61.9, D64.0, D66-D67, D68.0-D69.4, D69.6-D69.8, D70-D70.0, D70.4-D75.8, D76-D77, D86.8, D89-D89.2, E03-E03.1, E03.3-E06.3, E06.5-E07.1, E16.1-E16.9, E20-E23.0, E23.2-E24.1, E24.3, E24.8-E27.2, E27.4-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>E34</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, E34.1-E34.8, E65-E66.0, E66.2-E68, E70-E85.2, E88-E88.2, E88.4-E88.9, G71.2, N10-N12.9, N13.6, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>N15</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, N15.1-N16.8, N20-N23.0, N25-N28.1, N29-N30.3, N30.8-N32.0, N32.3-N32.4, N34-N34.3, N36-N36.9, N39-N39.2, N41-N41.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>N44</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">-N44.0, N45-N45.9, N49-N49.9, N60-N60.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>N72</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-N72.0, N75-N77.8, N80-N81.9, N83-N83.9, N84.0-N84.1, N87-N87.9, P72.1, P96.0, Q00-Q07.9, Q10.4-Q18.9, Q20-Q28.9, Q30-Q45.9, Q50-Q56.4, Q60-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Q86</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, Q86.8-Q87.8, Q89-Q89.8, Q90-Q93.9, Q95-Q99.8, R95-R95.9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A40-A41.9, A48.0, A48.3, A49.0-A49.1, A59-A59.9, A71-A71.9, A74.0, B07-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>B07.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, B30-B30.9, B35-B36.9, B85-B85.4, B87-B88.9, B94.0, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D50</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-D50.0, D50.9, D62-D63.0, D63.8-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D64</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, D64.1-D65.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D68</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D69.9, E15</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-E16</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, E50-E50.9, E64.1, E85.3-E87.6, E87.8-E87.9, F19-F19.9, G06-G08.0, G32-G32.8, G43-G44.2, G44.4-G44.8, G47-G47.2, G47.4-G47.9, G50-G60.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>G62</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-G62.0, G62.2-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>G65.2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, G80-G83.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>G89-G89.4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, G91-G91.2, G91.4-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>G93</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, G93.1-G93.2, G93.4-G93.6, G94.0-G94.8, G99-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>H05</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, H05.2-H69.9, H71-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>H99</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, I26-I26.9, I31.2-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I31.4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, I46-I46.9, I50.0-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I50.4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I76</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, I91-I91.1, I95-I95.1, I95.8-I95.9, J69-J69.9, J80-J80.9, J81.0, J85-J85.3, J86-J86.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J90</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-J90.0, J93-J93.1, J93.8-J94.9, J96-J96.9, J98.1-J98.3, K00-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>K19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>K30</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, K65-K66.1, K66.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>K68.1-K68.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, K71-K71.6, K71.8-K72.9, K75.0, L20-L30.9, L40-L50.9, L52-L54.8, L56-L56.2, L56.4-L56.5, L57-L57.9, L59-L68.9, L70-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>L76.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, L80-L87.9, L90-L92.9, L94-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>L96</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, L98.5-L99.8, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>M04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, M10-M12.0, M12.2-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>M29</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>M37-M39</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, M43.2-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>M49</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, M49.2-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>M64</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, M65.1-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>M71</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, M71.2-M72.4, M72.8-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>M73</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, M73.8-M79.9, M83-M86.2, M86.5-M86.9, M87.2-M87.9, M89.1-M89.4, M90-M99.9, N17-N17.9, N19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-N19.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, N32.1-N32.2, N32.8-N33.8, N35-N35.9, N37-N37.8, N39.3-N39.8, N42-N43.4, N44.1-N44.8, N46-N48.9, N50-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>N53.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, N61-N64.9, N82-N82.9, N91-N91.5, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>N95</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, N95.1-N95.9, N97-N97.9, R02-R02.9, R03.1-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>R04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, R04.1-R04.9, R07.0, R08-R12.0, R14-R19.6, R19.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-R23</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, R23.1-R30.9, R32-R50.1, R50.8-R57.9, R58.0-R72.9, R74-R78, R78.6-R94.8, R96-R99.9, U05, U08-U49, U51-U81, U90-U99, X40-X44.9, X46-X46.9, X49-X49.9, Y10-Y14.9, Y16-Y19.9, Z00-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Z15.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Z17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-unsp.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A14.9, A29</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">-A30.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A45-A45.9, A47-A48</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, A48.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-A49</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, A49.3-A49.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A61-A62, A72-A73, A76</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, A97, B08-B09, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>B11-B14, B28-B29, B31-B32.4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, B34-B34.1, B34.3-B34.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>B61-B62</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, B68-B68.9, B73-B74.2, B76-B76.9, B79-B81.8, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>B84</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, B92-B94, B94.8-B94.9, B95.6-B97.1, B97.3, B97.7-B99.9, F07.2, F17-F17.9, G44.3, G91.3, G93.0, G93.3, I10-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I10.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, I15-I15.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I27</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, I27.8-I27.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I50</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I50.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-I50.9, I67.4, I70-I70.1, I70.8-I70.9, I74</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-I75.8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J81</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J81.1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, K92.0-K92.2, N70-N71.9, N73-N74, N74.2-N74.8, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>R03</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">-R03.0, R04.0, R05-R06.9, R13-R13.9, R23.0, R58, S00-T99.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>U50, W47-W48, W63, W71-W72, W82, W95-W97, W98</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>X07</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, X55-X56, X59-X59.9, Y20-Y34.9, Y86-Y87, Y87.2, Y89, Y89.9, Y92-Y99.9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A01</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, A31-A31.9, A42-A44.9, A49.2, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A64</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">-A64.0, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">9-A99.0, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>B17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, B17.1, B17.8-B17.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>B19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-B19.0, B19.2-B19.9, B37-B46.9, B49</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-B49.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>B55</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, B55.1-B55.9, B58-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>B59.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, B89, B94.2, C14-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C14.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, C22.9, C26-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C29</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C35-C36</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, C39-C39.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C42</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, C46-C46.9, C55-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C55.9,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> C57.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C59</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, C63.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C68</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, C68.9, C74-C74.9, C75.9-C80.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C83</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, C83.9, C85.1, C85.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C87</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, C94.6, C97-D00.0, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D01</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D01.4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-D02</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D02.4-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D02.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D07,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> D07.3, D07.6-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D09</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D09.1, D09.7, D09.9-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D10</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, D10.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D13</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D13.9-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D14</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, D14.4, D17-D21.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D28</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D28.9-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D29</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D29.9-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D30</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D30.9, D36.0, D36.9-D37.0, D37.6-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D38</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D38.6-D39.0, D39.7, D39.9-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D40</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D40.9-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D41</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, D41.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D44</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, D44.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D48</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D48.7-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D49.1, D49.5, D49.7-D49.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D54</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, D75.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D79-D85</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D87-D88</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, D89.8-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>D99</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, E07.8-E08.9,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> E17-E19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, E34.0, E34.9-E35.8,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> E37-E39</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> E47-E49.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>E62, E69</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, E87.7, E90-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>E998</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, F04-F07.0, F07.8-F09.9, F20-F50, F50.8-F99.0, G09-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>G09.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>G15-G19, G21</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, G21.2, G21.4-G22.0, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>G27-G29, G33-G34, G38-G39., G42, G48-G49, G66-G69, G74-G79, G84-G88</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, G93.8-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>G94</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, G96-G96.9, G98-G98.9, I00.0, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I03-I04., I14-I14., I16-I19, I29-I29.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, I44-I45.9, I49-I49.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I51</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, I51.6-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I59</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I90, I91.9-I94</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, I</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>96-I96.9, I98.4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-I98.8, I99-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ID5.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, J02.9, J03.9, J04.3, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J06</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, J06.9, J40-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J40.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, J47-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J59</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J65</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">-J65.0, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J71-J79</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J81.9, J83, J85.9, J87-J89, J90.9, J93.6, J97</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-J98.0, J98.4-J99.8, K21-K21.9, K22.7, K31.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-K34, K39, K47-K49, K53-K54</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, K63-K63.4, K63.8-K63.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>K69</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, K70.4-K70.9,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> K78-K79, K84, K88-K89, K92</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, K92.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-K93</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> K96-K99</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>L06-L07, L09, L15-L19, L31-L39, L69, L77-L79, N09</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, N13-N13.5, N13.7-N13.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>N24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, N28.8-N28.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>N38</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, N39.9-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>N40.9, N54-N59, N66-N69, N78-N79, N84</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, N84.2-N86, N88-N90.9, N92-N94.9, N95.0, O08-O08.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O17-O19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, O27, O37-O39, O49-O59, O78-O79, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O93-O95.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> P06, P09</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> P16-P19.9, P30-P34.2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, P40-P49, P62-P69, P73-P75.0, P79-P82, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>P85-P89</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, P92-P92.9, P96.9-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>P99.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Q08</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">-Q10.3, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Q19, Q29-Q29</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Q46-Q49,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Q57, Q88</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Q89.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Q94</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Q99.9-R01.2, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>R07</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, R07.1-R07.9, R31-R31.9, X64-X64.9, X69-X69.9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">B16.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>B54</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-B54.0, B64, B82-B82.9, B83.9,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> C69</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, C69.9, C91.1, C91.4-C91.5, C91.7-C91.9, C92.7-C92.9, C93.2, C93.5-C93.7, C93.9, E12-E14.9, G00, G00.9-G02.1, G03.9, I37.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I42</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-I42.0, I42.9, I51.5, I64</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-I64.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I67</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, I67.8-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I68</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, I68.8-I69, I69.4-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>I69.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J07-J08</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, J15.9, J17-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J19.6</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J22-J29</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, J64-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>J64.9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>P23</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, P23.5-P23.9, R73-R73.9, V87-V87.1, V87.4-V88.1, V88.4-V89.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>V99</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-V99.0, X84-X84.9, Y09-Y09.9, Y85-Y85.9</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2680,6 +6499,13 @@
       <b/>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -3108,7 +6934,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>872</v>
+        <v>855</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3140,3387 +6966,3387 @@
         <v>6</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>856</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="63" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>72</v>
+        <v>858</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="63" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>141</v>
+        <v>859</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A86" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="168.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>243</v>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>861</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>387</v>
+      <c r="A144" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>862</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A166" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>453</v>
+      <c r="A166" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>863</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>483</v>
+        <v>473</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A176" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>864</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A197" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>536</v>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A197" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>865</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="B204" s="3" t="s">
-        <v>557</v>
+      <c r="A204" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>547</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A207" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>562</v>
+        <v>548</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A207" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>552</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A214" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>583</v>
+        <v>571</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A214" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A225" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>612</v>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="42" x14ac:dyDescent="0.25">
+      <c r="A225" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>866</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A231" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>630</v>
+        <v>617</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A231" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>867</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" ht="168.75" x14ac:dyDescent="0.25">
-      <c r="A234" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="B234" s="3" t="s">
-        <v>639</v>
+        <v>625</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A234" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>868</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" ht="348.75" x14ac:dyDescent="0.25">
-      <c r="A248" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="B248" s="3" t="s">
-        <v>681</v>
+        <v>666</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="337.5" x14ac:dyDescent="0.25">
+      <c r="A248" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>869</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" ht="146.25" x14ac:dyDescent="0.25">
-      <c r="A249" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>684</v>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" ht="147" x14ac:dyDescent="0.25">
+      <c r="A249" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="B249" s="7" t="s">
+        <v>870</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A250" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="B250" s="3" t="s">
-        <v>687</v>
+        <v>670</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" ht="388.5" x14ac:dyDescent="0.25">
+      <c r="A250" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>871</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>688</v>
+        <v>672</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>691</v>
+        <v>675</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="146.25" x14ac:dyDescent="0.25">
-      <c r="A252" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="B252" s="3" t="s">
-        <v>693</v>
+      <c r="A252" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>872</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>694</v>
+        <v>677</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>695</v>
+        <v>678</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>696</v>
+        <v>679</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>698</v>
+        <v>681</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>700</v>
+        <v>683</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>701</v>
+        <v>684</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>702</v>
+        <v>685</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>703</v>
+        <v>686</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>704</v>
+        <v>687</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>705</v>
+        <v>688</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>706</v>
+        <v>689</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>708</v>
+        <v>691</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>709</v>
+        <v>692</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>710</v>
+        <v>693</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>711</v>
+        <v>694</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>712</v>
+        <v>695</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>713</v>
+        <v>696</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>714</v>
+        <v>697</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>715</v>
+        <v>698</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
-        <v>716</v>
+        <v>699</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>717</v>
+        <v>700</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>718</v>
+        <v>701</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>719</v>
+        <v>702</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>720</v>
+        <v>703</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>721</v>
+        <v>704</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>723</v>
+        <v>706</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>727</v>
+        <v>710</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>729</v>
+        <v>712</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>730</v>
+        <v>713</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>731</v>
+        <v>714</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>733</v>
+        <v>716</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>735</v>
+        <v>718</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>736</v>
+        <v>719</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="180" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>737</v>
+        <v>720</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>738</v>
+        <v>721</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>739</v>
+        <v>722</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="101.25" x14ac:dyDescent="0.25">
-      <c r="A268" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="B268" s="3" t="s">
-        <v>741</v>
+      <c r="A268" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>724</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>743</v>
+        <v>726</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>744</v>
+        <v>727</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>745</v>
+        <v>728</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
-        <v>746</v>
+        <v>729</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>747</v>
+        <v>730</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>749</v>
+        <v>732</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>750</v>
+        <v>733</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>751</v>
+        <v>734</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
-        <v>752</v>
+        <v>735</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>753</v>
+        <v>736</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>754</v>
+        <v>737</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>755</v>
+        <v>738</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>756</v>
+        <v>739</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>757</v>
+        <v>740</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
-        <v>758</v>
+        <v>741</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>759</v>
+        <v>742</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>760</v>
+        <v>743</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>761</v>
+        <v>744</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" ht="146.25" x14ac:dyDescent="0.25">
-      <c r="A276" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="B276" s="3" t="s">
-        <v>765</v>
+        <v>746</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" ht="136.5" x14ac:dyDescent="0.25">
+      <c r="A276" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>748</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>766</v>
+        <v>749</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>767</v>
+        <v>750</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>768</v>
+        <v>751</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>769</v>
+        <v>752</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
-        <v>770</v>
+        <v>753</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>771</v>
+        <v>754</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>772</v>
+        <v>755</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>773</v>
+        <v>756</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>774</v>
+        <v>757</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>775</v>
+        <v>758</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
-        <v>776</v>
+        <v>759</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>777</v>
+        <v>760</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>778</v>
+        <v>761</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>779</v>
+        <v>762</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>780</v>
+        <v>763</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>781</v>
+        <v>764</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
-        <v>782</v>
+        <v>765</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>783</v>
+        <v>766</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>784</v>
+        <v>767</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>785</v>
+        <v>768</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>786</v>
+        <v>769</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>787</v>
+        <v>770</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
-        <v>788</v>
+        <v>771</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>789</v>
+        <v>772</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>790</v>
+        <v>773</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>791</v>
+        <v>774</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>792</v>
+        <v>775</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>793</v>
+        <v>776</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
-        <v>794</v>
+        <v>777</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>795</v>
+        <v>778</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>797</v>
+        <v>780</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>798</v>
+        <v>781</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>799</v>
+        <v>782</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>802</v>
+        <v>785</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>803</v>
+        <v>786</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>804</v>
+        <v>787</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>805</v>
+        <v>788</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
-        <v>806</v>
+        <v>789</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>807</v>
+        <v>790</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>808</v>
+        <v>791</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>809</v>
+        <v>792</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>810</v>
+        <v>793</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
-        <v>812</v>
+        <v>795</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>814</v>
+        <v>797</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>815</v>
+        <v>798</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>816</v>
+        <v>799</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>817</v>
+        <v>800</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
-        <v>818</v>
+        <v>801</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>819</v>
+        <v>802</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>820</v>
+        <v>803</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>821</v>
+        <v>804</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
-        <v>824</v>
+        <v>807</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>825</v>
+        <v>808</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>826</v>
+        <v>809</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>827</v>
+        <v>810</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>828</v>
+        <v>811</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>829</v>
+        <v>812</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" s="3" t="s">
-        <v>830</v>
-      </c>
-      <c r="B298" s="3" t="s">
-        <v>831</v>
+      <c r="A298" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>814</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>832</v>
+        <v>815</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>833</v>
+        <v>816</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>834</v>
+        <v>817</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>835</v>
+        <v>818</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
-        <v>836</v>
+        <v>819</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>837</v>
+        <v>820</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>838</v>
+        <v>821</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>839</v>
+        <v>822</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>840</v>
+        <v>823</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>841</v>
+        <v>824</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
-        <v>842</v>
+        <v>825</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>843</v>
+        <v>826</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>844</v>
+        <v>827</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>845</v>
+        <v>828</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>846</v>
+        <v>829</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>847</v>
+        <v>830</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
-        <v>848</v>
+        <v>831</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>850</v>
+        <v>833</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>852</v>
+      <c r="A305" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="B305" s="7" t="s">
+        <v>835</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>853</v>
+        <v>836</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
-        <v>854</v>
+        <v>837</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>855</v>
+        <v>838</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>856</v>
+        <v>839</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>857</v>
+        <v>840</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>858</v>
+        <v>841</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>859</v>
+        <v>842</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
-        <v>860</v>
+        <v>843</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>861</v>
+        <v>844</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>862</v>
+        <v>845</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" s="2" t="s">
-        <v>863</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>864</v>
+      <c r="A309" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="B309" s="7" t="s">
+        <v>847</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>865</v>
+        <v>848</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="B310" s="3" t="s">
-        <v>867</v>
+      <c r="A310" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>850</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>868</v>
+        <v>851</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
-        <v>869</v>
+        <v>852</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>870</v>
+        <v>853</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>871</v>
+        <v>854</v>
       </c>
     </row>
   </sheetData>
